--- a/penjualan_produk_2024.xlsx
+++ b/penjualan_produk_2024.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>803</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>204</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>345</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>697</v>
+        <v>721</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>529</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>725</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>516</v>
+        <v>799</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>618</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>455</v>
+        <v>973</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>357</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>767</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>731</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>250</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>529</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>308</v>
+        <v>877</v>
       </c>
     </row>
     <row r="17">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>183</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>644</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>623</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>764</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>892</v>
+        <v>841</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>442</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>553</v>
+        <v>642</v>
       </c>
     </row>
     <row r="24">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>705</v>
+        <v>857</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>948</v>
+        <v>812</v>
       </c>
     </row>
     <row r="26">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>353</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>580</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>964</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>184</v>
+        <v>786</v>
       </c>
     </row>
     <row r="30">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>708</v>
+        <v>745</v>
       </c>
     </row>
     <row r="31">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>311</v>
+        <v>838</v>
       </c>
     </row>
     <row r="32">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>971</v>
+        <v>581</v>
       </c>
     </row>
     <row r="33">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>422</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>863</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>531</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>723</v>
+        <v>622</v>
       </c>
     </row>
     <row r="37">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>388</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
